--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260611_215721.xlsx
@@ -5896,7 +5896,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
